--- a/docs/simulated-pilot-dataset/NJDL-JD-A1/00_manifest/dataset-manifest.xlsx
+++ b/docs/simulated-pilot-dataset/NJDL-JD-A1/00_manifest/dataset-manifest.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2d916bed5c2e14a47ebc5ad79f09c865ed2dcc5ce5a00dce5d496a88b7d0c6a1</t>
+          <t>609e27af585b177b9fa08d913f52f38c7d82683bc9b7de5883ad854d2ebc1fc6</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>a404729f49af2f337c542aebfff8f46d3b4f46f873b6484cc61245fbf6dbd265</t>
+          <t>968de29fdbecddcb75979959ee703c0e3fd49b838d43220734a14057308abc83</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>cfeab3de2627494c542442a064b715f406ec2da7d69acbd6c2d3ee4f69166d5e</t>
+          <t>e5cb0e8e2335a846a15c55b50f8db3682379b2b142ed0f4e9efcb403ad39a648</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8ff9aa8ca50b88b5f675a4909d009e8a0b663478b40fe124d027532c2b12df68</t>
+          <t>e44ce1571ece945b346ae4153d4af051a08418f9c1805bfdeb3f9539f75de8a7</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30cf27cc5bc26147712aa5ee72e580c59d10d44e3d5a71b5234a31c54fbfd4df</t>
+          <t>3cd1e9fda89d2b59cbfececdcb09ef7721ba041e3cac9a40175f071c12580696</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>e9fe6ea4c497f0e4cf17a0dff9e08710f6b3df72a06548a4366777ada0cce9ad</t>
+          <t>d6e3301ef0b4cd14204cee7d9eecfaff3c4d8c6a7498787f65b7b5b304f747ef</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3cbeff534ba4483e0ec94d018d3e193daa7bf9a2b5a84df186ac96e4482c03d5</t>
+          <t>fb3ccf8c01540e451ae1e10761ae5b9d15572e1215051672d12167cffe29ba47</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>d564345790fc0e9416cb95839d2c4722f8d26c8ca041b34884e49b89b0073d92</t>
+          <t>ae1b3bdf8d629a56ec63ceb26c91d9e04afdd0bcfccc13c1cc0151b207afd7d4</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>b7537f0c90ef53f1ea41dc917e70d5f54a8786194f98795cacd3383edda888ac</t>
+          <t>e71e304ed5d8366c89156d3a0f6335a6a5cd1a4126b74abe1aa74901e78ede8f</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9ba46c27d9f7e7de8a380f1c23f21e75da92b2425b717a7d51a7cbe84877139f</t>
+          <t>1886dbfaf196847f308990a8eb2beb23e2167b6c45b7d8653aeed2cb6c954720</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>d375e284c8fb86f9525a65fccb9f9871b322ca1219d80c6e2f59d3284c810c2e</t>
+          <t>1d28e2a92ef3812cf41c3a26cb03ec9ecbdfa47d18db6df41eba88c3a07cd8d4</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>55dfc2e49b7292c553e498b5942017052d9126de2a8a075070e23f04f991a398</t>
+          <t>40f8566076a1753b5edc6ed827b0b227922e8f89169c027431d9feb9fc131ceb</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>b8a4ab459caa826862aa331088de8ccfd6c41b6f366740e8f6c24460d1401ab7</t>
+          <t>6bdc7532ba1d786541f2ebd99779e82b05899c331fe4f7c594cc792d0d1085ea</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6815cc85488da41e44e8b9de2e8d06e1e5717d94402f2dd33d075a1223825e40</t>
+          <t>fb95b549240e0eb071ac4fb2da7d52ec56b906bfd9db1357dda6291e802456f5</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>362bac467ec76adb4c655bc47136eeb3e93b13e64d9033e12045a0d3117b2daa</t>
+          <t>da897158d15135fc805135e6aebb84b5afb37912a6dac1b325ba97dcd82ba569</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>234f4aad65fe0ed4d15a7b49a2be9cd1184ec943c27650259293f64657c068b6</t>
+          <t>3f8adf1301fe6f4c47b5007c2998f2907d44c3876b9a4f63c0768e8acb5a751b</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>104fc5f67b154eb93758f87f5bdd4e0900b5b7ada5102431ed71db27e97d39f2</t>
+          <t>c1f9b153a7b4bd7c86bde5bd73221e81eca9d31d93fcbe24dc9950b89f09c2ec</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>ea3a4f2f8f7bd803ce2298d85303c35f980e61690b625b405f5029f7cc525fb6</t>
+          <t>911615287d6d98a6eae4caaa3f50d38257a6a04eaa4205626e06bbe8c1cd841e</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>a02483fd448bbfaaf21db9259310a132e1c9735e09e9f459c9712f09fc7a44f0</t>
+          <t>4a73bfcf8f3c6f1e00d08d2c94fa7119dedf87f18209018da81d67c9832e5e5d</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>895c6b8625b09b8ecfd44bb33da9d2af31deb7f8cf487430e4053af161c0f5be</t>
+          <t>f1303b92a55f16ac16bd349b63d4ee5b327de3e1172743257cc06191e15c2a5d</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>c34dc72cc70bd6dd765c2af14b1e97ec248072b5ffc5bf6dbb2b474045f18cd7</t>
+          <t>b2c67727e77cfeaf3d23470e8dfdf96482da911015734f138e5e77652592e43f</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>800a3d3517a1984ff15039b864f2bd688f993b52e47db3dd2848ad7c82177d97</t>
+          <t>5beb5a6686343cb477591630ece9d3c0f0f668dbdbaa006df679337ad28e9f5a</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>629f1f25b8fad48bd5b829729d2db604e0122cd6454c056c16d2a69eb0c1817d</t>
+          <t>ec5786411a9f16ad997de30e90bdc18c8e27c41ec9a3e3c621e4a9ea7510194c</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1ba9958e2204731521c7007a4c9e078f87aee35e3632d487d9ef90ff23fecc77</t>
+          <t>fa33019d4088d06db35475713f03631ce277f957644d45d4bf13cbade0689dd8</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2f4d8af689133505dad6877e4fe4d985a8353609489b6804ff022e373c8b8975</t>
+          <t>04c5cb2dc06e4eb0d5f76f247c7dd7a634547ce31c48627c13b44c9c42f1a85f</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>53f792dfb164f4af3c5fc432eca426910e7e62d04787aa288cbd2cbdba266863</t>
+          <t>0ade571813fb4a418bfb2b5d6462079f72dd9736695174990c840f04e5c31ac0</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>9458cff6e0189c40f86043294b4666d2da55e3a0ab7ceda7a37e96d501acb6df</t>
+          <t>1dee0beab66677b57c4cd1168bf52e5ede6b2c6ac296273d048d297095712e74</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>01d69f12d155611579e6ae4b5540ff0c8fca6e41d9122d22319bc9ac4998c345</t>
+          <t>87e230025f0cce5f12c13ed204be4daac0f6d3177c2803b747cca31fc9450b99</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>a55edbe66ac81c52a928202716e71710f4dfbc3c4a8621fd24cf199e99f2365e</t>
+          <t>1e8508374d7f64a3fe02e5b485ea8699f44325ab86392fdbee883614ae60a7fe</t>
         </is>
       </c>
     </row>
